--- a/artfynd/A 25218-2023 artfynd.xlsx
+++ b/artfynd/A 25218-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25218-2023 artfynd.xlsx
+++ b/artfynd/A 25218-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>31494</v>
       </c>
       <c r="B2" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588510.0864063551</v>
+        <v>588510</v>
       </c>
       <c r="R2" t="n">
-        <v>6311978.362504251</v>
+        <v>6311978</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>1990-04-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-04-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +769,275 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114307082</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56830</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>588515</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6311966</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>01:11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>01:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>. Calluna AB. .</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122254536</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>588650</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6312030</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>01:13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>01:14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25218-2023 artfynd.xlsx
+++ b/artfynd/A 25218-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/31494</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114307082</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,8 +1053,18 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122254536</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>